--- a/Team-Data/2014-15/3-2-2014-15.xlsx
+++ b/Team-Data/2014-15/3-2-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>6.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -778,7 +845,7 @@
         <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>21</v>
@@ -987,7 +1054,7 @@
         <v>25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -1025,43 +1092,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.431</v>
+        <v>0.421</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J4" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
         <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.325</v>
+        <v>0.322</v>
       </c>
       <c r="O4" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0.746</v>
@@ -1070,7 +1137,7 @@
         <v>10.1</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T4" t="n">
         <v>42.2</v>
@@ -1085,40 +1152,40 @@
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="n">
         <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
@@ -1130,10 +1197,10 @@
         <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
         <v>23</v>
@@ -1148,7 +1215,7 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
@@ -1169,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>18</v>
@@ -1178,7 +1245,7 @@
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>4</v>
@@ -1336,7 +1403,7 @@
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1482,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
@@ -1509,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1530,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -1652,31 +1719,31 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
         <v>12</v>
@@ -1685,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
@@ -1694,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0.656</v>
+        <v>0.639</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,40 +1838,40 @@
         <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K8" t="n">
         <v>0.462</v>
       </c>
       <c r="L8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
         <v>0.353</v>
       </c>
       <c r="O8" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
         <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
         <v>12.7</v>
@@ -1819,7 +1886,7 @@
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA8" t="n">
         <v>21.7</v>
@@ -1828,19 +1895,19 @@
         <v>105.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1876,7 +1943,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1891,16 +1958,16 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2049,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>22</v>
@@ -2228,10 +2295,10 @@
         <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
         <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.793</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2326,28 +2393,28 @@
         <v>10.6</v>
       </c>
       <c r="M11" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="N11" t="n">
         <v>0.389</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
         <v>21.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R11" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S11" t="n">
         <v>34.5</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
         <v>27.1</v>
@@ -2368,16 +2435,16 @@
         <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.1</v>
+        <v>110.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2386,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>25</v>
@@ -2419,13 +2486,13 @@
         <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2446,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,58 +2575,58 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S12" t="n">
         <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>21.8</v>
       </c>
       <c r="V12" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,7 +2638,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
@@ -2592,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2607,34 +2674,34 @@
         <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-0.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2765,13 +2832,13 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>22</v>
@@ -2780,22 +2847,22 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.656</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,7 +2930,7 @@
         <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.472</v>
@@ -2872,22 +2939,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N14" t="n">
         <v>0.368</v>
       </c>
       <c r="O14" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P14" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.721</v>
+        <v>0.724</v>
       </c>
       <c r="R14" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S14" t="n">
         <v>32.7</v>
@@ -2905,13 +2972,13 @@
         <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>21.6</v>
@@ -2923,10 +2990,10 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2950,13 +3017,13 @@
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
         <v>4</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2971,7 +3038,7 @@
         <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>0.281</v>
+        <v>0.276</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
         <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
@@ -3135,22 +3202,22 @@
         <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
@@ -3168,16 +3235,16 @@
         <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB15" t="n">
         <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>16</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3320,13 +3387,13 @@
         <v>21</v>
       </c>
       <c r="AO16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>4</v>
       </c>
       <c r="AR16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.441</v>
+        <v>0.431</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="J17" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
         <v>7.1</v>
       </c>
       <c r="M17" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.744</v>
@@ -3436,10 +3503,10 @@
         <v>8.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T17" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="U17" t="n">
         <v>20.2</v>
@@ -3448,7 +3515,7 @@
         <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3457,19 +3524,19 @@
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>94</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,22 +3557,22 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
         <v>19</v>
       </c>
       <c r="AM17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3535,16 +3602,16 @@
         <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3666,7 +3733,7 @@
         <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -3675,7 +3742,7 @@
         <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3690,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
@@ -3708,10 +3775,10 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
@@ -3785,55 +3852,55 @@
         <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O19" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R19" t="n">
         <v>12.3</v>
       </c>
       <c r="S19" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X19" t="n">
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
         <v>19.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
         <v>-7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3872,22 +3939,22 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV19" t="n">
         <v>24</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>8</v>
@@ -3902,7 +3969,7 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -3940,112 +4007,112 @@
         <v>59</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.525</v>
+        <v>0.542</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
@@ -4057,16 +4124,16 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU20" t="n">
         <v>15</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4084,10 +4151,10 @@
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
         <v>30</v>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4236,22 +4303,22 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
         <v>22</v>
@@ -4266,7 +4333,7 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4439,10 +4506,10 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.317</v>
+        <v>0.311</v>
       </c>
       <c r="H23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.352</v>
@@ -4525,19 +4592,19 @@
         <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
         <v>7.5</v>
@@ -4546,7 +4613,7 @@
         <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
@@ -4555,13 +4622,13 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4582,10 +4649,10 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,13 +4673,13 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>21</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="J24" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="L24" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M24" t="n">
         <v>24.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="O24" t="n">
         <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q24" t="n">
         <v>0.68</v>
@@ -4710,13 +4777,13 @@
         <v>11.4</v>
       </c>
       <c r="S24" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T24" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U24" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V24" t="n">
         <v>18.6</v>
@@ -4728,34 +4795,34 @@
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.6</v>
+        <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4791,28 +4858,28 @@
         <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
         <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.508</v>
+        <v>0.517</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
         <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="O25" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P25" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.773</v>
+        <v>0.776</v>
       </c>
       <c r="R25" t="n">
         <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T25" t="n">
         <v>43.1</v>
       </c>
       <c r="U25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
         <v>15.1</v>
@@ -4913,22 +4980,22 @@
         <v>4.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.7</v>
+        <v>105.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
@@ -4937,7 +5004,7 @@
         <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4952,34 +5019,34 @@
         <v>7</v>
       </c>
       <c r="AM25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW25" t="n">
         <v>6</v>
@@ -4994,13 +5061,13 @@
         <v>28</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5177,7 @@
         <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>6</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.603</v>
+        <v>0.61</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,43 +5478,43 @@
         <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O28" t="n">
         <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
@@ -5471,7 +5538,7 @@
         <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5480,10 +5547,10 @@
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
@@ -5492,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,31 +5568,31 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5534,19 +5601,19 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -5575,37 +5642,37 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
         <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>0.633</v>
+        <v>0.627</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J29" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O29" t="n">
         <v>19.7</v>
@@ -5614,7 +5681,7 @@
         <v>25.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
@@ -5623,10 +5690,10 @@
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U29" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V29" t="n">
         <v>13.2</v>
@@ -5641,31 +5708,31 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA29" t="n">
         <v>21</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>8</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="n">
         <v>8</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5674,7 +5741,7 @@
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,7 +5750,7 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5701,10 +5768,10 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -5865,10 +5932,10 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5877,7 +5944,7 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>24</v>
@@ -5907,7 +5974,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6083,7 +6150,7 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>19</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-2-2014-15</t>
+          <t>2015-03-02</t>
         </is>
       </c>
     </row>
